--- a/Documents/Data Science and Analytics Work Plan V1_1.xlsx
+++ b/Documents/Data Science and Analytics Work Plan V1_1.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="6636" windowHeight="3948" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="6636" windowHeight="3948"/>
   </bookViews>
   <sheets>
     <sheet name="Strategic Issue 3" sheetId="3" r:id="rId1"/>
@@ -513,9 +513,6 @@
     <t>System functional specifications, API documentations and UAT(User Acceptance Testing) sign-off</t>
   </si>
   <si>
-    <t>2. Data Collection, Analysis and Research Support Services+D15:H18D15:J18D15:K18D15:M1D15:Q18</t>
-  </si>
-  <si>
     <t>% of datasets with&lt;1% error rate ; completion rate</t>
   </si>
   <si>
@@ -2057,6 +2054,9 @@
   </si>
   <si>
     <t>TOTAL CRITICAL ADDITIONS</t>
+  </si>
+  <si>
+    <t>2. Data Collection, Analysis and Research Support Services</t>
   </si>
 </sst>
 </file>
@@ -2317,60 +2317,6 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2390,6 +2336,60 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2734,7 +2734,7 @@
   <cols>
     <col min="1" max="1" width="9.19921875" style="8"/>
     <col min="2" max="2" width="9.19921875" style="14"/>
-    <col min="3" max="3" width="9.19921875" style="8"/>
+    <col min="3" max="3" width="52.19921875" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="16.5" style="19" customWidth="1"/>
     <col min="7" max="7" width="20" style="20" customWidth="1"/>
     <col min="8" max="9" width="19.796875" style="8" customWidth="1"/>
@@ -2750,106 +2750,106 @@
   <sheetData>
     <row r="1" spans="2:27" ht="13.8" thickBot="1"/>
     <row r="2" spans="2:27" ht="13.8" thickBot="1">
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23"/>
-      <c r="W2" s="23"/>
-      <c r="X2" s="23"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="23"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
       <c r="AA2" s="15"/>
     </row>
     <row r="3" spans="2:27" ht="27" thickBot="1">
-      <c r="B3" s="24"/>
-      <c r="C3" s="25" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="45" t="s">
         <v>21</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="28" t="s">
+      <c r="K3" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="29" t="s">
+      <c r="L3" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="M3" s="29"/>
-      <c r="N3" s="29"/>
-      <c r="O3" s="29" t="s">
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="29"/>
-      <c r="Q3" s="29"/>
-      <c r="R3" s="29" t="s">
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="S3" s="29"/>
-      <c r="T3" s="29"/>
-      <c r="U3" s="29" t="s">
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="V3" s="29"/>
-      <c r="W3" s="29"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="47"/>
       <c r="X3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="Y3" s="28" t="s">
+      <c r="Y3" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="22" t="s">
+      <c r="Z3" s="46"/>
+      <c r="AA3" s="41" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="2:27" ht="15" customHeight="1" thickBot="1">
-      <c r="B4" s="24"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="45"/>
       <c r="F4" s="5"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="46"/>
       <c r="L4" s="4" t="s">
         <v>33</v>
       </c>
@@ -2895,73 +2895,73 @@
       <c r="Z4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="AA4" s="22"/>
+      <c r="AA4" s="41"/>
     </row>
     <row r="5" spans="2:27" s="14" customFormat="1" ht="13.8" thickBot="1">
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="31"/>
-      <c r="T5" s="31"/>
-      <c r="U5" s="31"/>
-      <c r="V5" s="31"/>
-      <c r="W5" s="31"/>
-      <c r="X5" s="31"/>
-      <c r="Y5" s="31"/>
-      <c r="Z5" s="31"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="36"/>
       <c r="AA5" s="1"/>
     </row>
     <row r="6" spans="2:27" s="14" customFormat="1" ht="13.8" thickBot="1">
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="31"/>
-      <c r="Y6" s="31"/>
-      <c r="Z6" s="31"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="36"/>
+      <c r="V6" s="36"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="36"/>
+      <c r="Y6" s="36"/>
+      <c r="Z6" s="36"/>
       <c r="AA6" s="1"/>
     </row>
     <row r="7" spans="2:27" s="14" customFormat="1" ht="13.8" thickBot="1">
-      <c r="B7" s="23">
+      <c r="B7" s="37">
         <v>4</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="38" t="s">
         <v>50</v>
       </c>
       <c r="D7" s="2"/>
@@ -2990,78 +2990,78 @@
       <c r="AA7" s="15"/>
     </row>
     <row r="8" spans="2:27" s="14" customFormat="1" ht="13.8" thickBot="1">
-      <c r="B8" s="23"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="33" t="s">
+      <c r="B8" s="37"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="33"/>
-      <c r="M8" s="33"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="33"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="33"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="33"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="39"/>
+      <c r="S8" s="39"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="39"/>
+      <c r="V8" s="39"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="39"/>
+      <c r="Y8" s="39"/>
+      <c r="Z8" s="39"/>
       <c r="AA8" s="15"/>
     </row>
     <row r="9" spans="2:27" ht="13.8" thickBot="1">
-      <c r="B9" s="23"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="30" t="s">
+      <c r="B9" s="37"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="30"/>
-      <c r="T9" s="30"/>
-      <c r="U9" s="30"/>
-      <c r="V9" s="30"/>
-      <c r="W9" s="30"/>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="30"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35"/>
       <c r="AA9" s="15"/>
     </row>
     <row r="10" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B10" s="23"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="34" t="s">
+      <c r="B10" s="37"/>
+      <c r="C10" s="38"/>
+      <c r="D10" s="30" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="35" t="s">
+      <c r="F10" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="36" t="s">
+      <c r="G10" s="40" t="s">
         <v>8</v>
       </c>
       <c r="H10" s="12" t="s">
@@ -3119,20 +3119,20 @@
       <c r="Z10" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="AA10" s="47">
+      <c r="AA10" s="29">
         <f>Sheet1!H3</f>
         <v>570000</v>
       </c>
     </row>
     <row r="11" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B11" s="23"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="34"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="30"/>
       <c r="E11" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="35"/>
-      <c r="G11" s="36"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="40"/>
       <c r="H11" s="12" t="s">
         <v>74</v>
       </c>
@@ -3191,19 +3191,19 @@
       <c r="AA11" s="15"/>
     </row>
     <row r="12" spans="2:27" ht="106.2" thickBot="1">
-      <c r="B12" s="23"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="34"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="30"/>
       <c r="E12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="35"/>
-      <c r="G12" s="36"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="40"/>
       <c r="H12" s="12" t="s">
         <v>75</v>
       </c>
       <c r="I12" s="12" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J12" s="12" t="s">
         <v>108</v>
@@ -3257,19 +3257,19 @@
       <c r="AA12" s="15"/>
     </row>
     <row r="13" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B13" s="23"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="34"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="30"/>
       <c r="E13" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="35"/>
-      <c r="G13" s="36"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="40"/>
       <c r="H13" s="12" t="s">
         <v>76</v>
       </c>
       <c r="I13" s="12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="J13" s="12" t="s">
         <v>122</v>
@@ -3296,7 +3296,7 @@
         <v>127</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="S13" s="16" t="s">
         <v>130</v>
@@ -3323,19 +3323,19 @@
       <c r="AA13" s="15"/>
     </row>
     <row r="14" spans="2:27" ht="53.4" thickBot="1">
-      <c r="B14" s="23"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="34"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="30"/>
       <c r="E14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="35"/>
-      <c r="G14" s="36"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="40"/>
       <c r="H14" s="12" t="s">
         <v>77</v>
       </c>
       <c r="I14" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="J14" s="12" t="s">
         <v>134</v>
@@ -3389,67 +3389,67 @@
       <c r="AA14" s="15"/>
     </row>
     <row r="15" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B15" s="23"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="34" t="s">
-        <v>152</v>
+      <c r="B15" s="37"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="30" t="s">
+        <v>543</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="35" t="s">
+      <c r="F15" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="36" t="s">
+      <c r="G15" s="40" t="s">
         <v>10</v>
       </c>
       <c r="H15" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="I15" s="12" t="s">
+      <c r="J15" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="K15" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="L15" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="M15" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="M15" s="11" t="s">
+      <c r="N15" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="N15" s="11" t="s">
+      <c r="O15" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="P15" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="P15" s="11" t="s">
+      <c r="Q15" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="Q15" s="11" t="s">
+      <c r="R15" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="R15" s="11" t="s">
+      <c r="S15" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="S15" s="11" t="s">
+      <c r="T15" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="T15" s="11" t="s">
+      <c r="U15" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="U15" s="11" t="s">
+      <c r="V15" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="V15" s="11" t="s">
+      <c r="W15" s="11" t="s">
         <v>167</v>
-      </c>
-      <c r="W15" s="11" t="s">
-        <v>168</v>
       </c>
       <c r="X15" s="11"/>
       <c r="Y15" s="11" t="s">
@@ -3461,61 +3461,61 @@
       <c r="AA15" s="15"/>
     </row>
     <row r="16" spans="2:27" ht="106.2" thickBot="1">
-      <c r="B16" s="23"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="34"/>
+      <c r="B16" s="37"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="30"/>
       <c r="E16" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="F16" s="35"/>
-      <c r="G16" s="36"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="40"/>
       <c r="H16" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="I16" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="I16" s="12" t="s">
+      <c r="J16" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="K16" s="12" t="s">
         <v>171</v>
       </c>
-      <c r="K16" s="12" t="s">
+      <c r="L16" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="M16" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="N16" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="O16" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="M16" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="N16" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="O16" s="11" t="s">
+      <c r="P16" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="P16" s="11" t="s">
+      <c r="Q16" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="Q16" s="11" t="s">
+      <c r="R16" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="R16" s="11" t="s">
+      <c r="S16" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="S16" s="11" t="s">
+      <c r="T16" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="T16" s="11" t="s">
+      <c r="U16" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="U16" s="11" t="s">
+      <c r="V16" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="V16" s="11" t="s">
+      <c r="W16" s="11" t="s">
         <v>183</v>
-      </c>
-      <c r="W16" s="11" t="s">
-        <v>184</v>
       </c>
       <c r="X16" s="11"/>
       <c r="Y16" s="11" t="s">
@@ -3527,61 +3527,61 @@
       <c r="AA16" s="15"/>
     </row>
     <row r="17" spans="2:27" ht="79.8" thickBot="1">
-      <c r="B17" s="23"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="34"/>
+      <c r="B17" s="37"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="30"/>
       <c r="E17" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="40"/>
       <c r="H17" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="I17" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="I17" s="12" t="s">
+      <c r="J17" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="K17" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="K17" s="12" t="s">
+      <c r="L17" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="M17" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="M17" s="11" t="s">
+      <c r="N17" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="N17" s="11" t="s">
+      <c r="O17" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="O17" s="11" t="s">
+      <c r="P17" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="P17" s="11" t="s">
+      <c r="Q17" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="Q17" s="11" t="s">
+      <c r="R17" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="R17" s="11" t="s">
+      <c r="S17" s="11" t="s">
         <v>195</v>
       </c>
-      <c r="S17" s="11" t="s">
+      <c r="T17" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="T17" s="11" t="s">
+      <c r="U17" s="11" t="s">
         <v>197</v>
       </c>
-      <c r="U17" s="11" t="s">
+      <c r="V17" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="V17" s="11" t="s">
+      <c r="W17" s="11" t="s">
         <v>199</v>
-      </c>
-      <c r="W17" s="11" t="s">
-        <v>200</v>
       </c>
       <c r="X17" s="11"/>
       <c r="Y17" s="11" t="s">
@@ -3593,61 +3593,61 @@
       <c r="AA17" s="15"/>
     </row>
     <row r="18" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B18" s="23"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="34"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="30"/>
       <c r="E18" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="35"/>
-      <c r="G18" s="36"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="40"/>
       <c r="H18" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="I18" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="I18" s="12" t="s">
+      <c r="J18" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="K18" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="K18" s="12" t="s">
+      <c r="L18" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="M18" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="M18" s="11" t="s">
+      <c r="N18" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="N18" s="11" t="s">
+      <c r="O18" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="O18" s="11" t="s">
+      <c r="P18" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="P18" s="11" t="s">
+      <c r="Q18" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="Q18" s="11" t="s">
+      <c r="R18" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="R18" s="11" t="s">
+      <c r="S18" s="11" t="s">
         <v>211</v>
       </c>
-      <c r="S18" s="11" t="s">
+      <c r="T18" s="11" t="s">
         <v>212</v>
       </c>
-      <c r="T18" s="11" t="s">
+      <c r="U18" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="U18" s="11" t="s">
+      <c r="V18" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="V18" s="11" t="s">
+      <c r="W18" s="11" t="s">
         <v>215</v>
-      </c>
-      <c r="W18" s="11" t="s">
-        <v>216</v>
       </c>
       <c r="X18" s="11"/>
       <c r="Y18" s="11" t="s">
@@ -3659,67 +3659,67 @@
       <c r="AA18" s="15"/>
     </row>
     <row r="19" spans="2:27" ht="87.45" customHeight="1" thickBot="1">
-      <c r="B19" s="23"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="34" t="s">
+      <c r="B19" s="37"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="30" t="s">
         <v>11</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F19" s="35" t="s">
+      <c r="F19" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="37" t="s">
+      <c r="G19" s="32" t="s">
         <v>3</v>
       </c>
       <c r="H19" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="I19" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="I19" s="12" t="s">
+      <c r="J19" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="K19" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="K19" s="12" t="s">
+      <c r="L19" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="M19" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="M19" s="11" t="s">
+      <c r="N19" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="O19" s="11" t="s">
         <v>222</v>
-      </c>
-      <c r="N19" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="O19" s="11" t="s">
-        <v>223</v>
       </c>
       <c r="P19" s="11" t="s">
         <v>117</v>
       </c>
       <c r="Q19" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="R19" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="R19" s="11" t="s">
+      <c r="S19" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="S19" s="11" t="s">
+      <c r="T19" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="T19" s="11" t="s">
+      <c r="U19" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="U19" s="11" t="s">
+      <c r="V19" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="V19" s="11" t="s">
+      <c r="W19" s="11" t="s">
         <v>229</v>
-      </c>
-      <c r="W19" s="11" t="s">
-        <v>230</v>
       </c>
       <c r="X19" s="11"/>
       <c r="Y19" s="11" t="s">
@@ -3731,61 +3731,61 @@
       <c r="AA19" s="15"/>
     </row>
     <row r="20" spans="2:27" ht="53.4" thickBot="1">
-      <c r="B20" s="23"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="34"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="38"/>
+      <c r="D20" s="30"/>
       <c r="E20" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="35"/>
-      <c r="G20" s="38"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="33"/>
       <c r="H20" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="I20" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="I20" s="12" t="s">
+      <c r="J20" s="12" t="s">
         <v>232</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="K20" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="L20" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="M20" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="M20" s="11" t="s">
+      <c r="N20" s="11" t="s">
         <v>236</v>
       </c>
-      <c r="N20" s="11" t="s">
+      <c r="O20" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="O20" s="11" t="s">
+      <c r="P20" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="P20" s="11" t="s">
+      <c r="Q20" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="Q20" s="11" t="s">
+      <c r="R20" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="S20" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="R20" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="S20" s="11" t="s">
+      <c r="T20" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="T20" s="11" t="s">
+      <c r="U20" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="V20" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="U20" s="11" t="s">
-        <v>238</v>
-      </c>
-      <c r="V20" s="11" t="s">
+      <c r="W20" s="11" t="s">
         <v>243</v>
-      </c>
-      <c r="W20" s="11" t="s">
-        <v>244</v>
       </c>
       <c r="X20" s="11"/>
       <c r="Y20" s="11" t="s">
@@ -3797,61 +3797,61 @@
       <c r="AA20" s="15"/>
     </row>
     <row r="21" spans="2:27" ht="79.8" thickBot="1">
-      <c r="B21" s="23"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="34"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="38"/>
+      <c r="D21" s="30"/>
       <c r="E21" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="F21" s="35"/>
-      <c r="G21" s="38"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="33"/>
       <c r="H21" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="I21" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="I21" s="12" t="s">
+      <c r="J21" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="K21" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="K21" s="12" t="s">
+      <c r="L21" s="11" t="s">
         <v>248</v>
-      </c>
-      <c r="L21" s="11" t="s">
-        <v>249</v>
       </c>
       <c r="M21" s="11" t="s">
         <v>117</v>
       </c>
       <c r="N21" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="O21" s="11" t="s">
         <v>250</v>
       </c>
-      <c r="O21" s="11" t="s">
+      <c r="P21" s="11" t="s">
         <v>251</v>
       </c>
-      <c r="P21" s="11" t="s">
+      <c r="Q21" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="Q21" s="11" t="s">
+      <c r="R21" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="R21" s="11" t="s">
+      <c r="S21" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="S21" s="11" t="s">
+      <c r="T21" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="T21" s="11" t="s">
+      <c r="U21" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="U21" s="11" t="s">
+      <c r="V21" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="V21" s="11" t="s">
+      <c r="W21" s="11" t="s">
         <v>258</v>
-      </c>
-      <c r="W21" s="11" t="s">
-        <v>259</v>
       </c>
       <c r="X21" s="11"/>
       <c r="Y21" s="11" t="s">
@@ -3863,61 +3863,61 @@
       <c r="AA21" s="15"/>
     </row>
     <row r="22" spans="2:27" ht="53.4" thickBot="1">
-      <c r="B22" s="23"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="34"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="38"/>
+      <c r="D22" s="30"/>
       <c r="E22" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F22" s="35"/>
-      <c r="G22" s="39"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="34"/>
       <c r="H22" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="I22" s="12" t="s">
         <v>260</v>
       </c>
-      <c r="I22" s="12" t="s">
+      <c r="J22" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="K22" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="K22" s="12" t="s">
+      <c r="L22" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="M22" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="M22" s="11" t="s">
+      <c r="N22" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="N22" s="11" t="s">
+      <c r="O22" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="P22" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="O22" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="P22" s="11" t="s">
+      <c r="Q22" s="11" t="s">
         <v>267</v>
       </c>
-      <c r="Q22" s="11" t="s">
+      <c r="R22" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="R22" s="11" t="s">
+      <c r="S22" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="S22" s="11" t="s">
+      <c r="T22" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="T22" s="11" t="s">
+      <c r="U22" s="11" t="s">
         <v>271</v>
       </c>
-      <c r="U22" s="11" t="s">
+      <c r="V22" s="11" t="s">
         <v>272</v>
       </c>
-      <c r="V22" s="11" t="s">
+      <c r="W22" s="11" t="s">
         <v>273</v>
-      </c>
-      <c r="W22" s="11" t="s">
-        <v>274</v>
       </c>
       <c r="X22" s="11"/>
       <c r="Y22" s="11" t="s">
@@ -3929,271 +3929,271 @@
       <c r="AA22" s="15"/>
     </row>
     <row r="23" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B23" s="23"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="34" t="s">
+      <c r="B23" s="37"/>
+      <c r="C23" s="38"/>
+      <c r="D23" s="30" t="s">
         <v>13</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="F23" s="35" t="s">
+      <c r="F23" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="G23" s="37" t="s">
+      <c r="G23" s="32" t="s">
         <v>14</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="J23" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="K23" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="K23" s="12" t="s">
+      <c r="L23" s="11" t="s">
         <v>277</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="M23" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="N23" s="11" t="s">
         <v>278</v>
       </c>
-      <c r="M23" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="N23" s="11" t="s">
+      <c r="O23" s="11" t="s">
         <v>279</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>280</v>
       </c>
       <c r="P23" s="11" t="s">
         <v>117</v>
       </c>
       <c r="Q23" s="11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R23" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="S23" s="11" t="s">
         <v>143</v>
       </c>
       <c r="T23" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="U23" s="11" t="s">
+        <v>213</v>
+      </c>
+      <c r="V23" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="U23" s="11" t="s">
-        <v>214</v>
-      </c>
-      <c r="V23" s="11" t="s">
+      <c r="W23" s="11" t="s">
         <v>283</v>
-      </c>
-      <c r="W23" s="11" t="s">
-        <v>284</v>
       </c>
       <c r="X23" s="11"/>
       <c r="Y23" s="11" t="s">
         <v>91</v>
       </c>
       <c r="Z23" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA23" s="15"/>
     </row>
     <row r="24" spans="2:27" ht="117.45" customHeight="1" thickBot="1">
-      <c r="B24" s="23"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="34"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="38"/>
+      <c r="D24" s="30"/>
       <c r="E24" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="35"/>
-      <c r="G24" s="38"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="33"/>
       <c r="H24" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="I24" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="I24" s="12" t="s">
+      <c r="J24" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="K24" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="L24" s="11" t="s">
         <v>289</v>
       </c>
-      <c r="K24" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="L24" s="11" t="s">
+      <c r="M24" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="M24" s="11" t="s">
+      <c r="N24" s="11" t="s">
         <v>291</v>
       </c>
-      <c r="N24" s="11" t="s">
+      <c r="O24" s="11" t="s">
         <v>292</v>
       </c>
-      <c r="O24" s="11" t="s">
+      <c r="P24" s="11" t="s">
         <v>293</v>
       </c>
-      <c r="P24" s="11" t="s">
+      <c r="Q24" s="11" t="s">
         <v>294</v>
       </c>
-      <c r="Q24" s="11" t="s">
+      <c r="R24" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="S24" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="R24" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="S24" s="11" t="s">
+      <c r="T24" s="11" t="s">
         <v>296</v>
       </c>
-      <c r="T24" s="11" t="s">
+      <c r="U24" s="11" t="s">
         <v>297</v>
       </c>
-      <c r="U24" s="11" t="s">
+      <c r="V24" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="V24" s="11" t="s">
+      <c r="W24" s="11" t="s">
         <v>299</v>
-      </c>
-      <c r="W24" s="11" t="s">
-        <v>300</v>
       </c>
       <c r="X24" s="11"/>
       <c r="Y24" s="11" t="s">
         <v>91</v>
       </c>
       <c r="Z24" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA24" s="15"/>
     </row>
     <row r="25" spans="2:27" ht="79.8" thickBot="1">
-      <c r="B25" s="23"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="34"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="38"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="35"/>
-      <c r="G25" s="39"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="34"/>
       <c r="H25" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="I25" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="I25" s="12" t="s">
+      <c r="J25" s="12" t="s">
         <v>302</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="K25" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="K25" s="12" t="s">
+      <c r="L25" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="M25" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="M25" s="11" t="s">
+      <c r="N25" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="N25" s="11" t="s">
+      <c r="O25" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="O25" s="11" t="s">
+      <c r="P25" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="P25" s="11" t="s">
+      <c r="Q25" s="11" t="s">
         <v>309</v>
       </c>
-      <c r="Q25" s="11" t="s">
+      <c r="R25" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="R25" s="11" t="s">
+      <c r="S25" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="S25" s="11" t="s">
+      <c r="T25" s="11" t="s">
         <v>312</v>
       </c>
-      <c r="T25" s="11" t="s">
+      <c r="U25" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="U25" s="11" t="s">
+      <c r="V25" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="V25" s="11" t="s">
+      <c r="W25" s="11" t="s">
         <v>315</v>
-      </c>
-      <c r="W25" s="11" t="s">
-        <v>316</v>
       </c>
       <c r="X25" s="11"/>
       <c r="Y25" s="11" t="s">
         <v>91</v>
       </c>
       <c r="Z25" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AA25" s="15"/>
     </row>
     <row r="26" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B26" s="23"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="34" t="s">
+      <c r="B26" s="37"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="30" t="s">
         <v>16</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="35" t="s">
+      <c r="F26" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="37" t="s">
+      <c r="G26" s="32" t="s">
         <v>18</v>
       </c>
       <c r="H26" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="I26" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="J26" s="12" t="s">
         <v>318</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="K26" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="L26" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="K26" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="L26" s="11" t="s">
+      <c r="M26" s="11" t="s">
         <v>320</v>
-      </c>
-      <c r="M26" s="11" t="s">
-        <v>321</v>
       </c>
       <c r="N26" s="11" t="s">
         <v>117</v>
       </c>
       <c r="O26" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="P26" s="11" t="s">
         <v>322</v>
       </c>
-      <c r="P26" s="11" t="s">
+      <c r="Q26" s="11" t="s">
         <v>323</v>
       </c>
-      <c r="Q26" s="11" t="s">
+      <c r="R26" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="R26" s="11" t="s">
+      <c r="S26" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="S26" s="11" t="s">
+      <c r="T26" s="11" t="s">
+        <v>224</v>
+      </c>
+      <c r="U26" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="T26" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="U26" s="11" t="s">
+      <c r="V26" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="V26" s="11" t="s">
+      <c r="W26" s="11" t="s">
         <v>328</v>
-      </c>
-      <c r="W26" s="11" t="s">
-        <v>329</v>
       </c>
       <c r="X26" s="11"/>
       <c r="Y26" s="11" t="s">
@@ -4205,61 +4205,61 @@
       <c r="AA26" s="15"/>
     </row>
     <row r="27" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B27" s="23"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="34"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F27" s="35"/>
-      <c r="G27" s="38"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="33"/>
       <c r="H27" s="11" t="s">
+        <v>329</v>
+      </c>
+      <c r="I27" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="J27" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="J27" s="11" t="s">
+      <c r="K27" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="L27" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="M27" s="11" t="s">
         <v>334</v>
-      </c>
-      <c r="M27" s="11" t="s">
-        <v>335</v>
       </c>
       <c r="N27" s="11" t="s">
         <v>138</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="P27" s="11" t="s">
         <v>140</v>
       </c>
       <c r="Q27" s="11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="R27" s="11" t="s">
         <v>141</v>
       </c>
       <c r="S27" s="11" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="T27" s="11" t="s">
         <v>111</v>
       </c>
       <c r="U27" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="V27" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="V27" s="11" t="s">
-        <v>339</v>
-      </c>
       <c r="W27" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="X27" s="11"/>
       <c r="Y27" s="11" t="s">
@@ -4271,210 +4271,221 @@
       <c r="AA27" s="15"/>
     </row>
     <row r="28" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B28" s="23"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="34"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="38"/>
+      <c r="D28" s="30"/>
       <c r="E28" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F28" s="35"/>
-      <c r="G28" s="38"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="33"/>
       <c r="H28" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="I28" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="J28" s="11" t="s">
         <v>341</v>
       </c>
-      <c r="J28" s="11" t="s">
+      <c r="K28" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="L28" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="M28" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="M28" s="11" t="s">
+      <c r="N28" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="O28" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="N28" s="11" t="s">
-        <v>208</v>
-      </c>
-      <c r="O28" s="11" t="s">
+      <c r="P28" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="P28" s="11" t="s">
+      <c r="Q28" s="11" t="s">
+        <v>210</v>
+      </c>
+      <c r="R28" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="Q28" s="11" t="s">
-        <v>211</v>
-      </c>
-      <c r="R28" s="11" t="s">
+      <c r="S28" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="S28" s="11" t="s">
+      <c r="T28" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="T28" s="11" t="s">
+      <c r="U28" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="U28" s="11" t="s">
+      <c r="V28" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="V28" s="11" t="s">
+      <c r="W28" s="11" t="s">
         <v>352</v>
-      </c>
-      <c r="W28" s="11" t="s">
-        <v>353</v>
       </c>
       <c r="X28" s="11"/>
       <c r="Y28" s="11" t="s">
         <v>91</v>
       </c>
       <c r="Z28" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AA28" s="15"/>
     </row>
     <row r="29" spans="2:27" ht="66.599999999999994" thickBot="1">
-      <c r="B29" s="23"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="34"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F29" s="35"/>
-      <c r="G29" s="38"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="11" t="s">
+        <v>354</v>
+      </c>
+      <c r="I29" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="J29" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="J29" s="11" t="s">
+      <c r="K29" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="K29" s="11" t="s">
+      <c r="L29" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="L29" s="11" t="s">
+      <c r="M29" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="M29" s="11" t="s">
+      <c r="N29" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="N29" s="11" t="s">
+      <c r="O29" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="O29" s="11" t="s">
+      <c r="P29" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="P29" s="11" t="s">
+      <c r="Q29" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="R29" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="Q29" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="R29" s="11" t="s">
+      <c r="S29" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="T29" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="T29" s="11" t="s">
+      <c r="U29" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="U29" s="11" t="s">
+      <c r="V29" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="V29" s="11" t="s">
+      <c r="W29" s="11" t="s">
         <v>368</v>
-      </c>
-      <c r="W29" s="11" t="s">
-        <v>369</v>
       </c>
       <c r="X29" s="11"/>
       <c r="Y29" s="11" t="s">
         <v>91</v>
       </c>
       <c r="Z29" s="11" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AA29" s="15"/>
     </row>
     <row r="30" spans="2:27" ht="51.45" customHeight="1" thickBot="1">
-      <c r="B30" s="23"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="34"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="30"/>
       <c r="E30" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="35"/>
-      <c r="G30" s="39"/>
+      <c r="F30" s="31"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="I30" s="13" t="s">
         <v>370</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="J30" s="13" t="s">
         <v>371</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="K30" s="13" t="s">
         <v>372</v>
       </c>
-      <c r="K30" s="13" t="s">
+      <c r="L30" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="L30" s="13" t="s">
+      <c r="M30" s="13" t="s">
         <v>374</v>
       </c>
-      <c r="M30" s="13" t="s">
+      <c r="N30" s="13" t="s">
         <v>375</v>
       </c>
-      <c r="N30" s="13" t="s">
+      <c r="O30" s="13" t="s">
         <v>376</v>
       </c>
-      <c r="O30" s="13" t="s">
+      <c r="P30" s="13" t="s">
         <v>377</v>
       </c>
-      <c r="P30" s="13" t="s">
+      <c r="Q30" s="13" t="s">
         <v>378</v>
       </c>
-      <c r="Q30" s="13" t="s">
+      <c r="R30" s="13" t="s">
         <v>379</v>
       </c>
-      <c r="R30" s="13" t="s">
+      <c r="S30" s="13" t="s">
         <v>380</v>
       </c>
-      <c r="S30" s="13" t="s">
+      <c r="T30" s="13" t="s">
         <v>381</v>
       </c>
-      <c r="T30" s="13" t="s">
+      <c r="U30" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="U30" s="13" t="s">
+      <c r="V30" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="V30" s="13" t="s">
+      <c r="W30" s="13" t="s">
         <v>384</v>
-      </c>
-      <c r="W30" s="13" t="s">
-        <v>385</v>
       </c>
       <c r="X30" s="17"/>
       <c r="Y30" s="13" t="s">
         <v>91</v>
       </c>
       <c r="Z30" s="13" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AA30" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="D23:D25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G26:G30"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="G19:G22"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="B2:Z2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="O3:Q3"/>
+    <mergeCell ref="R3:T3"/>
+    <mergeCell ref="U3:W3"/>
+    <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="D9:Z9"/>
     <mergeCell ref="B5:Z5"/>
     <mergeCell ref="B6:Z6"/>
@@ -4491,22 +4502,11 @@
     <mergeCell ref="G15:G18"/>
     <mergeCell ref="D26:D30"/>
     <mergeCell ref="F26:F30"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="B2:Z2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="E3:E4"/>
-    <mergeCell ref="G3:G4"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="I3:I4"/>
-    <mergeCell ref="J3:J4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="O3:Q3"/>
-    <mergeCell ref="R3:T3"/>
-    <mergeCell ref="U3:W3"/>
-    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="G26:G30"/>
+    <mergeCell ref="G23:G25"/>
+    <mergeCell ref="G19:G22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -4528,1156 +4528,1156 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" thickBot="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="28" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>393</v>
       </c>
-      <c r="C1" s="46" t="s">
+      <c r="D1" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="D1" s="46" t="s">
+      <c r="E1" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="F1" s="28" t="s">
         <v>396</v>
       </c>
-      <c r="F1" s="46" t="s">
-        <v>397</v>
-      </c>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="28" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="42" thickBot="1">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="24" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" s="23" t="s">
         <v>403</v>
       </c>
-      <c r="B2" s="41" t="s">
+      <c r="C2" s="23" t="s">
         <v>404</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="D2" s="23" t="s">
         <v>405</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="E2" s="23">
+        <v>2</v>
+      </c>
+      <c r="F2" s="26">
+        <v>85000</v>
+      </c>
+      <c r="G2" s="26">
+        <v>170000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42" thickBot="1">
+      <c r="A3" s="23"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23" t="s">
         <v>406</v>
       </c>
-      <c r="E2" s="41">
-        <v>2</v>
-      </c>
-      <c r="F2" s="44">
-        <v>85000</v>
-      </c>
-      <c r="G2" s="44">
-        <v>170000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="42" thickBot="1">
-      <c r="A3" s="41"/>
-      <c r="B3" s="41"/>
-      <c r="C3" s="41" t="s">
+      <c r="D3" s="23" t="s">
         <v>407</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>408</v>
-      </c>
-      <c r="E3" s="41">
+      <c r="E3" s="23">
         <v>1</v>
       </c>
-      <c r="F3" s="44">
+      <c r="F3" s="26">
         <v>400000</v>
       </c>
-      <c r="G3" s="44">
+      <c r="G3" s="26">
         <v>400000</v>
       </c>
-      <c r="H3" s="43">
+      <c r="H3" s="25">
         <f>SUM(G2:G3)</f>
         <v>570000</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="55.8" thickBot="1">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="B4" s="23" t="s">
         <v>409</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="C4" s="23" t="s">
         <v>410</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="D4" s="23" t="s">
         <v>411</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="E4" s="23">
+        <v>1</v>
+      </c>
+      <c r="F4" s="26">
+        <v>250000</v>
+      </c>
+      <c r="G4" s="26">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42" thickBot="1">
+      <c r="A5" s="23"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23" t="s">
         <v>412</v>
       </c>
-      <c r="E4" s="41">
-        <v>1</v>
-      </c>
-      <c r="F4" s="44">
-        <v>250000</v>
-      </c>
-      <c r="G4" s="44">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="42" thickBot="1">
-      <c r="A5" s="41"/>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41" t="s">
+      <c r="D5" s="23" t="s">
         <v>413</v>
       </c>
-      <c r="D5" s="41" t="s">
-        <v>414</v>
-      </c>
-      <c r="E5" s="41">
+      <c r="E5" s="23">
         <v>4</v>
       </c>
-      <c r="F5" s="44">
+      <c r="F5" s="26">
         <v>30000</v>
       </c>
-      <c r="G5" s="44">
+      <c r="G5" s="26">
         <v>120000</v>
       </c>
-      <c r="H5" s="43">
+      <c r="H5" s="25">
         <f>SUM(G4:G5)</f>
         <v>370000</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="55.8" thickBot="1">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>415</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="C6" s="23" t="s">
         <v>416</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="D6" s="24" t="s">
         <v>417</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="E6" s="23">
+        <v>5</v>
+      </c>
+      <c r="F6" s="26">
+        <v>185000</v>
+      </c>
+      <c r="G6" s="26">
+        <v>925000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="42" thickBot="1">
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23" t="s">
         <v>418</v>
       </c>
-      <c r="E6" s="41">
+      <c r="D7" s="24" t="s">
+        <v>419</v>
+      </c>
+      <c r="E7" s="23">
+        <v>10</v>
+      </c>
+      <c r="F7" s="26">
+        <v>36000</v>
+      </c>
+      <c r="G7" s="26">
+        <v>360000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="55.8" thickBot="1">
+      <c r="A8" s="23"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="E8" s="23">
         <v>5</v>
       </c>
-      <c r="F6" s="44">
+      <c r="F8" s="26">
+        <v>15000</v>
+      </c>
+      <c r="G8" s="26">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="42" thickBot="1">
+      <c r="A9" s="23"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="E9" s="23">
+        <v>10</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>424</v>
+      </c>
+      <c r="G9" s="26">
         <v>185000</v>
       </c>
-      <c r="G6" s="44">
+    </row>
+    <row r="10" spans="1:8" ht="55.8" thickBot="1">
+      <c r="A10" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>427</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="E10" s="23">
+        <v>1</v>
+      </c>
+      <c r="F10" s="26">
+        <v>650000</v>
+      </c>
+      <c r="G10" s="26">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="55.8" thickBot="1">
+      <c r="A11" s="23"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>430</v>
+      </c>
+      <c r="E11" s="23">
+        <v>60</v>
+      </c>
+      <c r="F11" s="26">
+        <v>7500</v>
+      </c>
+      <c r="G11" s="26">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="55.8" thickBot="1">
+      <c r="A12" s="23"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>432</v>
+      </c>
+      <c r="E12" s="23">
+        <v>1</v>
+      </c>
+      <c r="F12" s="26">
+        <v>250000</v>
+      </c>
+      <c r="G12" s="26">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="42" thickBot="1">
+      <c r="A13" s="24" t="s">
+        <v>433</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>434</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>400</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>435</v>
+      </c>
+      <c r="E13" s="23">
+        <v>1</v>
+      </c>
+      <c r="F13" s="26">
+        <v>550000</v>
+      </c>
+      <c r="G13" s="26">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="55.8" thickBot="1">
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>437</v>
+      </c>
+      <c r="E14" s="23">
+        <v>5</v>
+      </c>
+      <c r="F14" s="26">
+        <v>185000</v>
+      </c>
+      <c r="G14" s="26">
         <v>925000</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" thickBot="1">
-      <c r="A7" s="41"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41" t="s">
-        <v>419</v>
-      </c>
-      <c r="D7" s="42" t="s">
-        <v>420</v>
-      </c>
-      <c r="E7" s="41">
+    <row r="15" spans="1:8" ht="42" thickBot="1">
+      <c r="A15" s="24" t="s">
+        <v>438</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>440</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>441</v>
+      </c>
+      <c r="E15" s="23">
         <v>10</v>
       </c>
-      <c r="F7" s="44">
-        <v>36000</v>
-      </c>
-      <c r="G7" s="44">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="55.8" thickBot="1">
-      <c r="A8" s="41"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41" t="s">
-        <v>421</v>
-      </c>
-      <c r="D8" s="42" t="s">
-        <v>422</v>
-      </c>
-      <c r="E8" s="41">
+      <c r="F15" s="26">
+        <v>14000</v>
+      </c>
+      <c r="G15" s="26">
+        <v>140000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="42" thickBot="1">
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23" t="s">
+        <v>442</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>443</v>
+      </c>
+      <c r="E16" s="23">
         <v>5</v>
       </c>
-      <c r="F8" s="44">
-        <v>15000</v>
-      </c>
-      <c r="G8" s="44">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="42" thickBot="1">
-      <c r="A9" s="41"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="41" t="s">
-        <v>423</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>424</v>
-      </c>
-      <c r="E9" s="41">
+      <c r="F16" s="26">
+        <v>11500</v>
+      </c>
+      <c r="G16" s="26">
+        <v>57500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="42" thickBot="1">
+      <c r="A17" s="24" t="s">
+        <v>444</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>445</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>446</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="E17" s="23">
+        <v>5</v>
+      </c>
+      <c r="F17" s="26">
+        <v>143000</v>
+      </c>
+      <c r="G17" s="26">
+        <v>715000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="42" thickBot="1">
+      <c r="A18" s="23"/>
+      <c r="B18" s="23"/>
+      <c r="C18" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>449</v>
+      </c>
+      <c r="E18" s="23">
+        <v>3</v>
+      </c>
+      <c r="F18" s="26">
+        <v>140000</v>
+      </c>
+      <c r="G18" s="26">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="42" thickBot="1">
+      <c r="A19" s="24" t="s">
+        <v>450</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>451</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>452</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>453</v>
+      </c>
+      <c r="E19" s="23">
         <v>10</v>
       </c>
-      <c r="F9" s="41" t="s">
-        <v>425</v>
-      </c>
-      <c r="G9" s="44">
+      <c r="F19" s="26">
+        <v>10500</v>
+      </c>
+      <c r="G19" s="26">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="42" thickBot="1">
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23" t="s">
+        <v>454</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="E20" s="23">
+        <v>10</v>
+      </c>
+      <c r="F20" s="26">
+        <v>12500</v>
+      </c>
+      <c r="G20" s="26">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="42" thickBot="1">
+      <c r="A21" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>457</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>458</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="E21" s="23">
+        <v>5</v>
+      </c>
+      <c r="F21" s="26">
+        <v>180000</v>
+      </c>
+      <c r="G21" s="26">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="42" thickBot="1">
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>461</v>
+      </c>
+      <c r="E22" s="23">
+        <v>12</v>
+      </c>
+      <c r="F22" s="26">
+        <v>25000</v>
+      </c>
+      <c r="G22" s="26">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="42" thickBot="1">
+      <c r="A23" s="24" t="s">
+        <v>462</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>463</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>464</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="E23" s="23">
+        <v>5</v>
+      </c>
+      <c r="F23" s="26">
         <v>185000</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="55.8" thickBot="1">
-      <c r="A10" s="42" t="s">
-        <v>426</v>
-      </c>
-      <c r="B10" s="41" t="s">
-        <v>427</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>428</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>429</v>
-      </c>
-      <c r="E10" s="41">
-        <v>1</v>
-      </c>
-      <c r="F10" s="44">
-        <v>650000</v>
-      </c>
-      <c r="G10" s="44">
-        <v>650000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="55.8" thickBot="1">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="41" t="s">
-        <v>430</v>
-      </c>
-      <c r="D11" s="42" t="s">
-        <v>431</v>
-      </c>
-      <c r="E11" s="41">
-        <v>60</v>
-      </c>
-      <c r="F11" s="44">
-        <v>7500</v>
-      </c>
-      <c r="G11" s="44">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="55.8" thickBot="1">
-      <c r="A12" s="41"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="41" t="s">
-        <v>432</v>
-      </c>
-      <c r="D12" s="42" t="s">
-        <v>433</v>
-      </c>
-      <c r="E12" s="41">
-        <v>1</v>
-      </c>
-      <c r="F12" s="44">
-        <v>250000</v>
-      </c>
-      <c r="G12" s="44">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="42" thickBot="1">
-      <c r="A13" s="42" t="s">
-        <v>434</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>435</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>401</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>436</v>
-      </c>
-      <c r="E13" s="41">
-        <v>1</v>
-      </c>
-      <c r="F13" s="44">
-        <v>550000</v>
-      </c>
-      <c r="G13" s="44">
-        <v>550000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="55.8" thickBot="1">
-      <c r="A14" s="41"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="41" t="s">
-        <v>437</v>
-      </c>
-      <c r="D14" s="42" t="s">
-        <v>438</v>
-      </c>
-      <c r="E14" s="41">
+      <c r="G23" s="26">
+        <v>925000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="42" thickBot="1">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="E24" s="23">
+        <v>10</v>
+      </c>
+      <c r="F24" s="26">
+        <v>18500</v>
+      </c>
+      <c r="G24" s="26">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="42" thickBot="1">
+      <c r="A25" s="24" t="s">
+        <v>468</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="E25" s="23">
         <v>5</v>
       </c>
-      <c r="F14" s="44">
+      <c r="F25" s="26">
+        <v>14000</v>
+      </c>
+      <c r="G25" s="26">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="42" thickBot="1">
+      <c r="A26" s="24" t="s">
+        <v>472</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>475</v>
+      </c>
+      <c r="E26" s="23">
+        <v>3</v>
+      </c>
+      <c r="F26" s="26">
+        <v>170000</v>
+      </c>
+      <c r="G26" s="26">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="42" thickBot="1">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>477</v>
+      </c>
+      <c r="E27" s="23">
+        <v>5</v>
+      </c>
+      <c r="F27" s="26">
+        <v>180000</v>
+      </c>
+      <c r="G27" s="26">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A28" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>479</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="E28" s="23">
+        <v>10</v>
+      </c>
+      <c r="F28" s="26">
+        <v>10500</v>
+      </c>
+      <c r="G28" s="26">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="42" thickBot="1">
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="E29" s="23">
+        <v>10</v>
+      </c>
+      <c r="F29" s="26">
+        <v>12500</v>
+      </c>
+      <c r="G29" s="26">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="42" thickBot="1">
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="E30" s="23">
+        <v>12</v>
+      </c>
+      <c r="F30" s="26">
+        <v>25000</v>
+      </c>
+      <c r="G30" s="26">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="42" thickBot="1">
+      <c r="A31" s="24" t="s">
+        <v>485</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="C31" s="23" t="s">
+        <v>487</v>
+      </c>
+      <c r="D31" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="E31" s="23">
+        <v>5</v>
+      </c>
+      <c r="F31" s="26">
         <v>185000</v>
       </c>
-      <c r="G14" s="44">
+      <c r="G31" s="26">
         <v>925000</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="42" thickBot="1">
-      <c r="A15" s="42" t="s">
-        <v>439</v>
-      </c>
-      <c r="B15" s="41" t="s">
-        <v>440</v>
-      </c>
-      <c r="C15" s="41" t="s">
-        <v>441</v>
-      </c>
-      <c r="D15" s="42" t="s">
+    <row r="32" spans="1:7" ht="42" thickBot="1">
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23" t="s">
+        <v>466</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="E32" s="23">
+        <v>10</v>
+      </c>
+      <c r="F32" s="26">
+        <v>18500</v>
+      </c>
+      <c r="G32" s="26">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="42" thickBot="1">
+      <c r="A33" s="24" t="s">
+        <v>489</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>490</v>
+      </c>
+      <c r="C33" s="23" t="s">
         <v>442</v>
       </c>
-      <c r="E15" s="41">
+      <c r="D33" s="24" t="s">
+        <v>491</v>
+      </c>
+      <c r="E33" s="23">
+        <v>5</v>
+      </c>
+      <c r="F33" s="26">
+        <v>14000</v>
+      </c>
+      <c r="G33" s="26">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23" t="s">
+        <v>492</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>493</v>
+      </c>
+      <c r="E34" s="23">
+        <v>3</v>
+      </c>
+      <c r="F34" s="26">
+        <v>170000</v>
+      </c>
+      <c r="G34" s="26">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A35" s="24" t="s">
+        <v>494</v>
+      </c>
+      <c r="B35" s="23" t="s">
+        <v>495</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="E35" s="23">
         <v>10</v>
       </c>
-      <c r="F15" s="44">
+      <c r="F35" s="26">
+        <v>10500</v>
+      </c>
+      <c r="G35" s="26">
+        <v>105000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="42" thickBot="1">
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23" t="s">
+        <v>482</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="E36" s="23">
+        <v>10</v>
+      </c>
+      <c r="F36" s="26">
+        <v>12500</v>
+      </c>
+      <c r="G36" s="26">
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="42" thickBot="1">
+      <c r="A37" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="D37" s="24" t="s">
+        <v>499</v>
+      </c>
+      <c r="E37" s="23">
+        <v>5</v>
+      </c>
+      <c r="F37" s="26">
+        <v>180000</v>
+      </c>
+      <c r="G37" s="26">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="42" thickBot="1">
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="E38" s="23">
+        <v>12</v>
+      </c>
+      <c r="F38" s="26">
+        <v>25000</v>
+      </c>
+      <c r="G38" s="26">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A39" s="24" t="s">
+        <v>500</v>
+      </c>
+      <c r="B39" s="23" t="s">
+        <v>501</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="D39" s="24" t="s">
+        <v>503</v>
+      </c>
+      <c r="E39" s="23">
+        <v>3</v>
+      </c>
+      <c r="F39" s="26">
+        <v>170000</v>
+      </c>
+      <c r="G39" s="26">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="42" thickBot="1">
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="D40" s="24" t="s">
+        <v>488</v>
+      </c>
+      <c r="E40" s="23">
+        <v>10</v>
+      </c>
+      <c r="F40" s="26">
+        <v>18500</v>
+      </c>
+      <c r="G40" s="26">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="42" thickBot="1">
+      <c r="A41" s="24" t="s">
+        <v>505</v>
+      </c>
+      <c r="B41" s="23" t="s">
+        <v>506</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>507</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="E41" s="23">
+        <v>5</v>
+      </c>
+      <c r="F41" s="26">
+        <v>185000</v>
+      </c>
+      <c r="G41" s="26">
+        <v>925000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="42" thickBot="1">
+      <c r="A42" s="23"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23" t="s">
+        <v>508</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>509</v>
+      </c>
+      <c r="E42" s="23">
+        <v>5</v>
+      </c>
+      <c r="F42" s="26">
         <v>14000</v>
       </c>
-      <c r="G15" s="44">
-        <v>140000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="42" thickBot="1">
-      <c r="A16" s="41"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="41" t="s">
-        <v>443</v>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>444</v>
-      </c>
-      <c r="E16" s="41">
+      <c r="G42" s="26">
+        <v>70000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="55.8" thickBot="1">
+      <c r="A43" s="24" t="s">
+        <v>510</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>511</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="D43" s="24" t="s">
+        <v>513</v>
+      </c>
+      <c r="E43" s="23">
         <v>5</v>
       </c>
-      <c r="F16" s="44">
-        <v>11500</v>
-      </c>
-      <c r="G16" s="44">
-        <v>57500</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="42" thickBot="1">
-      <c r="A17" s="42" t="s">
-        <v>445</v>
-      </c>
-      <c r="B17" s="41" t="s">
-        <v>446</v>
-      </c>
-      <c r="C17" s="41" t="s">
-        <v>447</v>
-      </c>
-      <c r="D17" s="42" t="s">
-        <v>448</v>
-      </c>
-      <c r="E17" s="41">
-        <v>5</v>
-      </c>
-      <c r="F17" s="44">
-        <v>143000</v>
-      </c>
-      <c r="G17" s="44">
-        <v>715000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="42" thickBot="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="41" t="s">
-        <v>449</v>
-      </c>
-      <c r="D18" s="42" t="s">
-        <v>450</v>
-      </c>
-      <c r="E18" s="41">
-        <v>3</v>
-      </c>
-      <c r="F18" s="44">
-        <v>140000</v>
-      </c>
-      <c r="G18" s="44">
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="42" thickBot="1">
-      <c r="A19" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="B19" s="41" t="s">
-        <v>452</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>453</v>
-      </c>
-      <c r="D19" s="42" t="s">
-        <v>454</v>
-      </c>
-      <c r="E19" s="41">
+      <c r="F43" s="26">
+        <v>180000</v>
+      </c>
+      <c r="G43" s="26">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A44" s="24" t="s">
+        <v>514</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>515</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>516</v>
+      </c>
+      <c r="D44" s="24" t="s">
+        <v>481</v>
+      </c>
+      <c r="E44" s="23">
         <v>10</v>
       </c>
-      <c r="F19" s="44">
+      <c r="F44" s="26">
         <v>10500</v>
       </c>
-      <c r="G19" s="44">
+      <c r="G44" s="26">
         <v>105000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="42" thickBot="1">
-      <c r="A20" s="41"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="41" t="s">
+    <row r="45" spans="1:7" ht="42" thickBot="1">
+      <c r="A45" s="24" t="s">
+        <v>517</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>518</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>519</v>
+      </c>
+      <c r="D45" s="24" t="s">
         <v>455</v>
       </c>
-      <c r="D20" s="42" t="s">
-        <v>456</v>
-      </c>
-      <c r="E20" s="41">
+      <c r="E45" s="23">
         <v>10</v>
       </c>
-      <c r="F20" s="44">
+      <c r="F45" s="26">
         <v>12500</v>
       </c>
-      <c r="G20" s="44">
+      <c r="G45" s="26">
         <v>125000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="42" thickBot="1">
-      <c r="A21" s="42" t="s">
-        <v>457</v>
-      </c>
-      <c r="B21" s="41" t="s">
-        <v>458</v>
-      </c>
-      <c r="C21" s="41" t="s">
-        <v>459</v>
-      </c>
-      <c r="D21" s="42" t="s">
-        <v>460</v>
-      </c>
-      <c r="E21" s="41">
-        <v>5</v>
-      </c>
-      <c r="F21" s="44">
-        <v>180000</v>
-      </c>
-      <c r="G21" s="44">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="42" thickBot="1">
-      <c r="A22" s="41"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="41" t="s">
-        <v>461</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>462</v>
-      </c>
-      <c r="E22" s="41">
+    <row r="46" spans="1:7" ht="42" thickBot="1">
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23" t="s">
+        <v>520</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>484</v>
+      </c>
+      <c r="E46" s="23">
         <v>12</v>
       </c>
-      <c r="F22" s="44">
+      <c r="F46" s="26">
         <v>25000</v>
       </c>
-      <c r="G22" s="44">
+      <c r="G46" s="26">
         <v>300000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="42" thickBot="1">
-      <c r="A23" s="42" t="s">
-        <v>463</v>
-      </c>
-      <c r="B23" s="41" t="s">
-        <v>464</v>
-      </c>
-      <c r="C23" s="41" t="s">
-        <v>465</v>
-      </c>
-      <c r="D23" s="42" t="s">
-        <v>466</v>
-      </c>
-      <c r="E23" s="41">
-        <v>5</v>
-      </c>
-      <c r="F23" s="44">
-        <v>185000</v>
-      </c>
-      <c r="G23" s="44">
-        <v>925000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="42" thickBot="1">
-      <c r="A24" s="41"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="41" t="s">
-        <v>467</v>
-      </c>
-      <c r="D24" s="42" t="s">
-        <v>468</v>
-      </c>
-      <c r="E24" s="41">
-        <v>10</v>
-      </c>
-      <c r="F24" s="44">
-        <v>18500</v>
-      </c>
-      <c r="G24" s="44">
-        <v>185000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="42" thickBot="1">
-      <c r="A25" s="42" t="s">
-        <v>469</v>
-      </c>
-      <c r="B25" s="41" t="s">
-        <v>470</v>
-      </c>
-      <c r="C25" s="41" t="s">
-        <v>471</v>
-      </c>
-      <c r="D25" s="42" t="s">
-        <v>472</v>
-      </c>
-      <c r="E25" s="41">
-        <v>5</v>
-      </c>
-      <c r="F25" s="44">
-        <v>14000</v>
-      </c>
-      <c r="G25" s="44">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="42" thickBot="1">
-      <c r="A26" s="42" t="s">
-        <v>473</v>
-      </c>
-      <c r="B26" s="41" t="s">
-        <v>474</v>
-      </c>
-      <c r="C26" s="41" t="s">
-        <v>475</v>
-      </c>
-      <c r="D26" s="42" t="s">
-        <v>476</v>
-      </c>
-      <c r="E26" s="41">
-        <v>3</v>
-      </c>
-      <c r="F26" s="44">
-        <v>170000</v>
-      </c>
-      <c r="G26" s="44">
-        <v>510000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="42" thickBot="1">
-      <c r="A27" s="41"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="41" t="s">
-        <v>477</v>
-      </c>
-      <c r="D27" s="42" t="s">
-        <v>478</v>
-      </c>
-      <c r="E27" s="41">
-        <v>5</v>
-      </c>
-      <c r="F27" s="44">
-        <v>180000</v>
-      </c>
-      <c r="G27" s="44">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="28.2" thickBot="1">
-      <c r="A28" s="42" t="s">
-        <v>479</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>480</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>481</v>
-      </c>
-      <c r="D28" s="42" t="s">
-        <v>482</v>
-      </c>
-      <c r="E28" s="41">
-        <v>10</v>
-      </c>
-      <c r="F28" s="44">
-        <v>10500</v>
-      </c>
-      <c r="G28" s="44">
-        <v>105000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="42" thickBot="1">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41" t="s">
-        <v>483</v>
-      </c>
-      <c r="D29" s="42" t="s">
-        <v>456</v>
-      </c>
-      <c r="E29" s="41">
-        <v>10</v>
-      </c>
-      <c r="F29" s="44">
-        <v>12500</v>
-      </c>
-      <c r="G29" s="44">
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="42" thickBot="1">
-      <c r="A30" s="41"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="41" t="s">
-        <v>484</v>
-      </c>
-      <c r="D30" s="41" t="s">
-        <v>485</v>
-      </c>
-      <c r="E30" s="41">
-        <v>12</v>
-      </c>
-      <c r="F30" s="44">
-        <v>25000</v>
-      </c>
-      <c r="G30" s="44">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="42" thickBot="1">
-      <c r="A31" s="42" t="s">
-        <v>486</v>
-      </c>
-      <c r="B31" s="41" t="s">
-        <v>487</v>
-      </c>
-      <c r="C31" s="41" t="s">
-        <v>488</v>
-      </c>
-      <c r="D31" s="42" t="s">
-        <v>466</v>
-      </c>
-      <c r="E31" s="41">
-        <v>5</v>
-      </c>
-      <c r="F31" s="44">
-        <v>185000</v>
-      </c>
-      <c r="G31" s="44">
-        <v>925000</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="42" thickBot="1">
-      <c r="A32" s="41"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41" t="s">
-        <v>467</v>
-      </c>
-      <c r="D32" s="42" t="s">
-        <v>489</v>
-      </c>
-      <c r="E32" s="41">
-        <v>10</v>
-      </c>
-      <c r="F32" s="44">
-        <v>18500</v>
-      </c>
-      <c r="G32" s="44">
-        <v>185000</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="42" thickBot="1">
-      <c r="A33" s="42" t="s">
-        <v>490</v>
-      </c>
-      <c r="B33" s="41" t="s">
-        <v>491</v>
-      </c>
-      <c r="C33" s="41" t="s">
-        <v>443</v>
-      </c>
-      <c r="D33" s="42" t="s">
-        <v>492</v>
-      </c>
-      <c r="E33" s="41">
-        <v>5</v>
-      </c>
-      <c r="F33" s="44">
-        <v>14000</v>
-      </c>
-      <c r="G33" s="44">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="55.8" thickBot="1">
-      <c r="A34" s="41"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="41" t="s">
-        <v>493</v>
-      </c>
-      <c r="D34" s="42" t="s">
-        <v>494</v>
-      </c>
-      <c r="E34" s="41">
-        <v>3</v>
-      </c>
-      <c r="F34" s="44">
-        <v>170000</v>
-      </c>
-      <c r="G34" s="44">
-        <v>510000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="28.2" thickBot="1">
-      <c r="A35" s="42" t="s">
-        <v>495</v>
-      </c>
-      <c r="B35" s="41" t="s">
-        <v>496</v>
-      </c>
-      <c r="C35" s="41" t="s">
-        <v>497</v>
-      </c>
-      <c r="D35" s="42" t="s">
-        <v>482</v>
-      </c>
-      <c r="E35" s="41">
-        <v>10</v>
-      </c>
-      <c r="F35" s="44">
-        <v>10500</v>
-      </c>
-      <c r="G35" s="44">
-        <v>105000</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="42" thickBot="1">
-      <c r="A36" s="41"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="41" t="s">
-        <v>483</v>
-      </c>
-      <c r="D36" s="42" t="s">
-        <v>456</v>
-      </c>
-      <c r="E36" s="41">
-        <v>10</v>
-      </c>
-      <c r="F36" s="44">
-        <v>12500</v>
-      </c>
-      <c r="G36" s="44">
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="42" thickBot="1">
-      <c r="A37" s="42" t="s">
-        <v>457</v>
-      </c>
-      <c r="B37" s="41" t="s">
-        <v>498</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>499</v>
-      </c>
-      <c r="D37" s="42" t="s">
-        <v>500</v>
-      </c>
-      <c r="E37" s="41">
-        <v>5</v>
-      </c>
-      <c r="F37" s="44">
-        <v>180000</v>
-      </c>
-      <c r="G37" s="44">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="42" thickBot="1">
-      <c r="A38" s="41"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="41" t="s">
-        <v>484</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>485</v>
-      </c>
-      <c r="E38" s="41">
-        <v>12</v>
-      </c>
-      <c r="F38" s="44">
-        <v>25000</v>
-      </c>
-      <c r="G38" s="44">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="55.8" thickBot="1">
-      <c r="A39" s="42" t="s">
-        <v>501</v>
-      </c>
-      <c r="B39" s="41" t="s">
-        <v>502</v>
-      </c>
-      <c r="C39" s="41" t="s">
-        <v>503</v>
-      </c>
-      <c r="D39" s="42" t="s">
-        <v>504</v>
-      </c>
-      <c r="E39" s="41">
-        <v>3</v>
-      </c>
-      <c r="F39" s="44">
-        <v>170000</v>
-      </c>
-      <c r="G39" s="44">
-        <v>510000</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="42" thickBot="1">
-      <c r="A40" s="41"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="41" t="s">
-        <v>505</v>
-      </c>
-      <c r="D40" s="42" t="s">
-        <v>489</v>
-      </c>
-      <c r="E40" s="41">
-        <v>10</v>
-      </c>
-      <c r="F40" s="44">
-        <v>18500</v>
-      </c>
-      <c r="G40" s="44">
-        <v>185000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="42" thickBot="1">
-      <c r="A41" s="42" t="s">
-        <v>506</v>
-      </c>
-      <c r="B41" s="41" t="s">
-        <v>507</v>
-      </c>
-      <c r="C41" s="41" t="s">
-        <v>508</v>
-      </c>
-      <c r="D41" s="42" t="s">
-        <v>466</v>
-      </c>
-      <c r="E41" s="41">
-        <v>5</v>
-      </c>
-      <c r="F41" s="44">
-        <v>185000</v>
-      </c>
-      <c r="G41" s="44">
-        <v>925000</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="42" thickBot="1">
-      <c r="A42" s="41"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="41" t="s">
-        <v>509</v>
-      </c>
-      <c r="D42" s="42" t="s">
-        <v>510</v>
-      </c>
-      <c r="E42" s="41">
-        <v>5</v>
-      </c>
-      <c r="F42" s="44">
-        <v>14000</v>
-      </c>
-      <c r="G42" s="44">
-        <v>70000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="55.8" thickBot="1">
-      <c r="A43" s="42" t="s">
-        <v>511</v>
-      </c>
-      <c r="B43" s="41" t="s">
-        <v>512</v>
-      </c>
-      <c r="C43" s="41" t="s">
-        <v>513</v>
-      </c>
-      <c r="D43" s="42" t="s">
-        <v>514</v>
-      </c>
-      <c r="E43" s="41">
-        <v>5</v>
-      </c>
-      <c r="F43" s="44">
-        <v>180000</v>
-      </c>
-      <c r="G43" s="44">
-        <v>900000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="28.2" thickBot="1">
-      <c r="A44" s="42" t="s">
-        <v>515</v>
-      </c>
-      <c r="B44" s="41" t="s">
-        <v>516</v>
-      </c>
-      <c r="C44" s="41" t="s">
-        <v>517</v>
-      </c>
-      <c r="D44" s="42" t="s">
-        <v>482</v>
-      </c>
-      <c r="E44" s="41">
-        <v>10</v>
-      </c>
-      <c r="F44" s="44">
-        <v>10500</v>
-      </c>
-      <c r="G44" s="44">
-        <v>105000</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="42" thickBot="1">
-      <c r="A45" s="42" t="s">
-        <v>518</v>
-      </c>
-      <c r="B45" s="41" t="s">
-        <v>519</v>
-      </c>
-      <c r="C45" s="41" t="s">
-        <v>520</v>
-      </c>
-      <c r="D45" s="42" t="s">
-        <v>456</v>
-      </c>
-      <c r="E45" s="41">
-        <v>10</v>
-      </c>
-      <c r="F45" s="44">
-        <v>12500</v>
-      </c>
-      <c r="G45" s="44">
-        <v>125000</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="42" thickBot="1">
-      <c r="A46" s="41"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="41" t="s">
+    <row r="47" spans="1:7">
+      <c r="A47" s="22" t="s">
         <v>521</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>485</v>
-      </c>
-      <c r="E46" s="41">
-        <v>12</v>
-      </c>
-      <c r="F46" s="44">
-        <v>25000</v>
-      </c>
-      <c r="G46" s="44">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="40" t="s">
-        <v>522</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="14.4" thickBot="1"/>
     <row r="49" spans="1:7" ht="28.2" thickBot="1">
-      <c r="A49" s="42" t="s">
+      <c r="A49" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="B49" s="42" t="s">
+      <c r="B49" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="42" t="s">
-        <v>394</v>
-      </c>
-      <c r="D49" s="42" t="s">
+      <c r="C49" s="24" t="s">
+        <v>393</v>
+      </c>
+      <c r="D49" s="24" t="s">
+        <v>522</v>
+      </c>
+      <c r="E49" s="24" t="s">
+        <v>395</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>401</v>
+      </c>
+      <c r="G49" s="24" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="42" thickBot="1">
+      <c r="A50" s="24" t="s">
         <v>523</v>
       </c>
-      <c r="E49" s="42" t="s">
-        <v>396</v>
-      </c>
-      <c r="F49" s="42" t="s">
-        <v>402</v>
-      </c>
-      <c r="G49" s="42" t="s">
+      <c r="B50" s="23" t="s">
+        <v>524</v>
+      </c>
+      <c r="C50" s="24" t="s">
+        <v>525</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>526</v>
+      </c>
+      <c r="E50" s="23">
+        <v>1</v>
+      </c>
+      <c r="F50" s="26">
+        <v>9680000</v>
+      </c>
+      <c r="G50" s="26">
+        <v>9680000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="42" thickBot="1">
+      <c r="A51" s="24" t="s">
+        <v>527</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>529</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>530</v>
+      </c>
+      <c r="E51" s="23">
+        <v>1</v>
+      </c>
+      <c r="F51" s="26">
+        <v>110000</v>
+      </c>
+      <c r="G51" s="26">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="42" thickBot="1">
+      <c r="A52" s="24" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="42" thickBot="1">
-      <c r="A50" s="42" t="s">
-        <v>524</v>
-      </c>
-      <c r="B50" s="41" t="s">
-        <v>525</v>
-      </c>
-      <c r="C50" s="42" t="s">
-        <v>526</v>
-      </c>
-      <c r="D50" s="41" t="s">
-        <v>527</v>
-      </c>
-      <c r="E50" s="41">
+      <c r="B52" s="23" t="s">
+        <v>528</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>531</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>532</v>
+      </c>
+      <c r="E52" s="23">
         <v>1</v>
       </c>
-      <c r="F50" s="44">
-        <v>9680000</v>
-      </c>
-      <c r="G50" s="44">
-        <v>9680000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="42" thickBot="1">
-      <c r="A51" s="42" t="s">
+      <c r="F52" s="26">
+        <v>250000</v>
+      </c>
+      <c r="G52" s="26">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="42" thickBot="1">
+      <c r="A53" s="24" t="s">
+        <v>399</v>
+      </c>
+      <c r="B53" s="23" t="s">
         <v>528</v>
       </c>
-      <c r="B51" s="41" t="s">
-        <v>529</v>
-      </c>
-      <c r="C51" s="42" t="s">
-        <v>530</v>
-      </c>
-      <c r="D51" s="41" t="s">
-        <v>531</v>
-      </c>
-      <c r="E51" s="41">
+      <c r="C53" s="24" t="s">
+        <v>533</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="E53" s="23">
         <v>1</v>
       </c>
-      <c r="F51" s="44">
-        <v>110000</v>
-      </c>
-      <c r="G51" s="44">
-        <v>110000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="42" thickBot="1">
-      <c r="A52" s="42" t="s">
-        <v>399</v>
-      </c>
-      <c r="B52" s="41" t="s">
-        <v>529</v>
-      </c>
-      <c r="C52" s="42" t="s">
-        <v>532</v>
-      </c>
-      <c r="D52" s="41" t="s">
-        <v>533</v>
-      </c>
-      <c r="E52" s="41">
+      <c r="F53" s="26">
+        <v>185000</v>
+      </c>
+      <c r="G53" s="26">
+        <v>185000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="42" thickBot="1">
+      <c r="A54" s="24" t="s">
+        <v>535</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>536</v>
+      </c>
+      <c r="C54" s="24" t="s">
+        <v>537</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>538</v>
+      </c>
+      <c r="E54" s="23">
+        <v>12</v>
+      </c>
+      <c r="F54" s="26">
+        <v>15000</v>
+      </c>
+      <c r="G54" s="26">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="42" thickBot="1">
+      <c r="A55" s="24" t="s">
+        <v>456</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>539</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>540</v>
+      </c>
+      <c r="D55" s="23" t="s">
+        <v>541</v>
+      </c>
+      <c r="E55" s="23">
         <v>1</v>
       </c>
-      <c r="F52" s="44">
-        <v>250000</v>
-      </c>
-      <c r="G52" s="44">
-        <v>250000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="42" thickBot="1">
-      <c r="A53" s="42" t="s">
-        <v>400</v>
-      </c>
-      <c r="B53" s="41" t="s">
-        <v>529</v>
-      </c>
-      <c r="C53" s="42" t="s">
-        <v>534</v>
-      </c>
-      <c r="D53" s="41" t="s">
-        <v>535</v>
-      </c>
-      <c r="E53" s="41">
-        <v>1</v>
-      </c>
-      <c r="F53" s="44">
-        <v>185000</v>
-      </c>
-      <c r="G53" s="44">
-        <v>185000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="42" thickBot="1">
-      <c r="A54" s="42" t="s">
-        <v>536</v>
-      </c>
-      <c r="B54" s="41" t="s">
-        <v>537</v>
-      </c>
-      <c r="C54" s="42" t="s">
-        <v>538</v>
-      </c>
-      <c r="D54" s="41" t="s">
-        <v>539</v>
-      </c>
-      <c r="E54" s="41">
-        <v>12</v>
-      </c>
-      <c r="F54" s="44">
-        <v>15000</v>
-      </c>
-      <c r="G54" s="44">
-        <v>180000</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="42" thickBot="1">
-      <c r="A55" s="42" t="s">
-        <v>457</v>
-      </c>
-      <c r="B55" s="41" t="s">
-        <v>540</v>
-      </c>
-      <c r="C55" s="42" t="s">
-        <v>541</v>
-      </c>
-      <c r="D55" s="41" t="s">
+      <c r="F55" s="26">
+        <v>450000</v>
+      </c>
+      <c r="G55" s="26">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="28.2" thickBot="1">
+      <c r="A56" s="24" t="s">
         <v>542</v>
       </c>
-      <c r="E55" s="41">
-        <v>1</v>
-      </c>
-      <c r="F55" s="44">
-        <v>450000</v>
-      </c>
-      <c r="G55" s="44">
-        <v>450000</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="28.2" thickBot="1">
-      <c r="A56" s="42" t="s">
-        <v>543</v>
-      </c>
-      <c r="B56" s="41"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="45">
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="27">
         <v>10855000</v>
       </c>
     </row>
